--- a/Devarim 5787.xlsx
+++ b/Devarim 5787.xlsx
@@ -2571,11 +2571,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Teitzei", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Teitzei&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -2612,7 +2612,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Teitzei&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Teitzei&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -2627,7 +2627,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Teitzei&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Teitzei&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -2642,7 +2642,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Teitzei&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Teitzei&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -2657,7 +2657,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Teitzei&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Teitzei&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -2672,7 +2672,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Teitzei&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Teitzei&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -2687,7 +2687,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Teitzei&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Teitzei&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -2702,7 +2702,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Teitzei&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Teitzei&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -2717,7 +2717,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Teitzei&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Teitzei&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -3083,11 +3083,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tavo", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tavo&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tavo&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tavo&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -3139,7 +3139,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tavo&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tavo&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -3154,7 +3154,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tavo&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tavo&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -3169,7 +3169,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tavo&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tavo&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -3184,7 +3184,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tavo&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tavo&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -3199,7 +3199,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tavo&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tavo&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -3214,7 +3214,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tavo&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tavo&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -3229,7 +3229,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tavo&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tavo&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -3595,11 +3595,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Nitzavim-Vayeilech", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Nitzavim-Vayeilech&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Nitzavim-Vayeilech&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Nitzavim-Vayeilech&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -3651,7 +3651,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Nitzavim-Vayeilech&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Nitzavim-Vayeilech&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -3666,7 +3666,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Nitzavim-Vayeilech&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Nitzavim-Vayeilech&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -3681,7 +3681,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Nitzavim-Vayeilech&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Nitzavim-Vayeilech&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -3696,7 +3696,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Nitzavim-Vayeilech&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Nitzavim-Vayeilech&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -3711,7 +3711,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Nitzavim-Vayeilech&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Nitzavim-Vayeilech&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -3726,7 +3726,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Nitzavim-Vayeilech&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Nitzavim-Vayeilech&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -3741,7 +3741,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Nitzavim-Vayeilech&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Nitzavim-Vayeilech&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -4107,11 +4107,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana I (on Shabbat)", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana I (on Shabbat)&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -4148,7 +4148,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana I (on Shabbat)&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana I (on Shabbat)&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -4163,7 +4163,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana I (on Shabbat)&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana I (on Shabbat)&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -4178,7 +4178,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana I (on Shabbat)&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana I (on Shabbat)&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -4193,7 +4193,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana I (on Shabbat)&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana I (on Shabbat)&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -4208,7 +4208,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana I (on Shabbat)&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana I (on Shabbat)&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -4223,7 +4223,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana I (on Shabbat)&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana I (on Shabbat)&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -4238,7 +4238,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana I (on Shabbat)&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana I (on Shabbat)&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -4253,7 +4253,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana I (on Shabbat)&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana I (on Shabbat)&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -4619,11 +4619,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana II", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana II&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -4660,7 +4660,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana II&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana II&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -4675,7 +4675,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana II&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana II&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -4690,7 +4690,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana II&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana II&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -4705,7 +4705,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana II&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana II&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -4720,7 +4720,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana II&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana II&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -4735,7 +4735,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana II&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Rosh Hashana II&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -5101,11 +5101,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzom Gedaliah", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzom Gedaliah&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -5142,7 +5142,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzom Gedaliah&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzom Gedaliah&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -5157,7 +5157,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzom Gedaliah&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzom Gedaliah&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -5172,7 +5172,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzom Gedaliah&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzom Gedaliah&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -5534,11 +5534,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzom Gedaliah (Mincha)", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzom Gedaliah (Mincha)&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzom Gedaliah (Mincha)&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzom Gedaliah (Mincha)&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -5590,7 +5590,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzom Gedaliah (Mincha)&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzom Gedaliah (Mincha)&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -5605,7 +5605,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzom Gedaliah (Mincha)&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzom Gedaliah (Mincha)&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -5975,11 +5975,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ha'azinu", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ha'azinu&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -6016,7 +6016,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ha'azinu&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ha'azinu&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -6031,7 +6031,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ha'azinu&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ha'azinu&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -6046,7 +6046,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ha'azinu&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ha'azinu&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -6061,7 +6061,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ha'azinu&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ha'azinu&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -6076,7 +6076,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ha'azinu&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ha'azinu&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -6091,7 +6091,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ha'azinu&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ha'azinu&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -6106,7 +6106,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ha'azinu&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ha'azinu&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -6121,7 +6121,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ha'azinu&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ha'azinu&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -6487,11 +6487,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -6528,7 +6528,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -6543,7 +6543,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -6558,7 +6558,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -6573,7 +6573,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -6588,7 +6588,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -6603,7 +6603,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -6618,7 +6618,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -6984,11 +6984,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur (Mincha)", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur (Mincha)&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -7025,7 +7025,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur (Mincha)&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur (Mincha)&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -7040,7 +7040,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur (Mincha)&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur (Mincha)&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -7055,7 +7055,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur (Mincha)&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom Kippur (Mincha)&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -7421,11 +7421,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Devarim", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Devarim&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -7462,7 +7462,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Devarim&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Devarim&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -7477,7 +7477,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Devarim&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Devarim&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -7492,7 +7492,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Devarim&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Devarim&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -7507,7 +7507,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Devarim&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Devarim&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -7522,7 +7522,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Devarim&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Devarim&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -7537,7 +7537,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Devarim&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Devarim&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -7552,7 +7552,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Devarim&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Devarim&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -7567,7 +7567,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Devarim&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Devarim&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -7933,11 +7933,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vezot Haberakhah", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vezot Haberakhah&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -8309,11 +8309,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot I (on Shabbat)", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot I (on Shabbat)&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -8350,7 +8350,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot I (on Shabbat)&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot I (on Shabbat)&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -8365,7 +8365,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot I (on Shabbat)&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot I (on Shabbat)&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -8380,7 +8380,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot I (on Shabbat)&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot I (on Shabbat)&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -8395,7 +8395,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot I (on Shabbat)&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot I (on Shabbat)&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -8410,7 +8410,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot I (on Shabbat)&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot I (on Shabbat)&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -8425,7 +8425,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot I (on Shabbat)&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot I (on Shabbat)&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -8440,7 +8440,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot I (on Shabbat)&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot I (on Shabbat)&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -8455,7 +8455,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot I (on Shabbat)&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot I (on Shabbat)&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -8821,11 +8821,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot II", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot II&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -8862,7 +8862,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot II&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot II&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -8877,7 +8877,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot II&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot II&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -8892,7 +8892,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot II&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot II&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -8907,7 +8907,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot II&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot II&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -8922,7 +8922,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot II&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot II&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -8937,7 +8937,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot II&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot II&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -9303,11 +9303,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot Final Day (Hoshana Raba)", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot Final Day (Hoshana Raba)&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -9344,7 +9344,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot Final Day (Hoshana Raba)&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot Final Day (Hoshana Raba)&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -9359,7 +9359,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot Final Day (Hoshana Raba)&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot Final Day (Hoshana Raba)&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -9374,7 +9374,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot Final Day (Hoshana Raba)&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot Final Day (Hoshana Raba)&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -9389,7 +9389,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot Final Day (Hoshana Raba)&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Sukkot Final Day (Hoshana Raba)&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -9751,11 +9751,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini Atzeret (on Shabbat)", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini Atzeret (on Shabbat)&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -9792,7 +9792,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini Atzeret (on Shabbat)&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini Atzeret (on Shabbat)&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -9807,7 +9807,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini Atzeret (on Shabbat)&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini Atzeret (on Shabbat)&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -9822,7 +9822,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini Atzeret (on Shabbat)&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini Atzeret (on Shabbat)&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -9837,7 +9837,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini Atzeret (on Shabbat)&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini Atzeret (on Shabbat)&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -9852,7 +9852,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini Atzeret (on Shabbat)&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini Atzeret (on Shabbat)&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -9867,7 +9867,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini Atzeret (on Shabbat)&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini Atzeret (on Shabbat)&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -9882,7 +9882,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini Atzeret (on Shabbat)&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini Atzeret (on Shabbat)&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -9897,7 +9897,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini Atzeret (on Shabbat)&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini Atzeret (on Shabbat)&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -10263,11 +10263,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Erev Simchat Torah", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Erev Simchat Torah&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -10304,7 +10304,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Erev Simchat Torah&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Erev Simchat Torah&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -10319,7 +10319,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Erev Simchat Torah&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Erev Simchat Torah&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -10334,7 +10334,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Erev Simchat Torah&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Erev Simchat Torah&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -10696,11 +10696,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Simchat Torah", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Simchat Torah&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -10737,7 +10737,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Simchat Torah&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Simchat Torah&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -10752,7 +10752,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Simchat Torah&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Simchat Torah&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -10767,7 +10767,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Simchat Torah&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Simchat Torah&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -10782,7 +10782,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Simchat Torah&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Simchat Torah&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -10797,7 +10797,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Simchat Torah&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Simchat Torah&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -10812,7 +10812,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Simchat Torah&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Simchat Torah&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -10827,7 +10827,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Simchat Torah&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Simchat Torah&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -10842,7 +10842,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Simchat Torah&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Simchat Torah&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -11208,11 +11208,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Erev Tish'a B'Av", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Erev Tish'a B'Av&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -11584,11 +11584,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tish'a B'Av", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tish'a B'Av&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -11625,7 +11625,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tish'a B'Av&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tish'a B'Av&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -11640,7 +11640,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tish'a B'Av&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tish'a B'Av&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -11655,7 +11655,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tish'a B'Av&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tish'a B'Av&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -12021,11 +12021,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tish'a B'Av (Mincha)", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tish'a B'Av (Mincha)&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -12062,7 +12062,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tish'a B'Av (Mincha)&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tish'a B'Av (Mincha)&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -12077,7 +12077,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tish'a B'Av (Mincha)&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tish'a B'Av (Mincha)&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -12092,7 +12092,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tish'a B'Av (Mincha)&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tish'a B'Av (Mincha)&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -12458,11 +12458,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaetchanan", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaetchanan&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -12499,7 +12499,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaetchanan&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaetchanan&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -12514,7 +12514,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaetchanan&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaetchanan&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -12529,7 +12529,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaetchanan&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaetchanan&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -12544,7 +12544,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaetchanan&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaetchanan&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -12559,7 +12559,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaetchanan&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaetchanan&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -12574,7 +12574,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaetchanan&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaetchanan&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -12589,7 +12589,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaetchanan&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaetchanan&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -12604,7 +12604,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaetchanan&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaetchanan&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -12970,11 +12970,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Eikev", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Eikev&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -13011,7 +13011,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Eikev&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Eikev&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -13026,7 +13026,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Eikev&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Eikev&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -13041,7 +13041,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Eikev&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Eikev&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -13056,7 +13056,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Eikev&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Eikev&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -13071,7 +13071,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Eikev&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Eikev&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -13086,7 +13086,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Eikev&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Eikev&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -13101,7 +13101,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Eikev&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Eikev&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -13116,7 +13116,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Eikev&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Eikev&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -13482,11 +13482,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Re'eh", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Re'eh&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -13523,7 +13523,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Re'eh&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Re'eh&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -13538,7 +13538,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Re'eh&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Re'eh&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -13553,7 +13553,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Re'eh&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Re'eh&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -13568,7 +13568,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Re'eh&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Re'eh&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -13583,7 +13583,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Re'eh&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Re'eh&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -13598,7 +13598,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Re'eh&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Re'eh&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -13613,7 +13613,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Re'eh&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Re'eh&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -13628,7 +13628,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Re'eh&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Re'eh&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -13994,11 +13994,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gunther</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shoftim", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shoftim&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -14035,7 +14035,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shoftim&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shoftim&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -14050,7 +14050,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shoftim&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shoftim&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -14065,7 +14065,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shoftim&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shoftim&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -14080,7 +14080,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shoftim&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shoftim&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -14095,7 +14095,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shoftim&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shoftim&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -14110,7 +14110,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shoftim&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shoftim&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -14125,7 +14125,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shoftim&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shoftim&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -14140,7 +14140,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shoftim&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shoftim&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
